--- a/Models/Лошади/results/Лошади - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/Лошади/results/Лошади - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72.89</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>58.63</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4.46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>247.19</v>
+        <v>269.24</v>
       </c>
       <c r="C3" t="n">
-        <v>209.54</v>
+        <v>222.54</v>
       </c>
       <c r="D3" t="n">
-        <v>10.82</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>554.2</v>
+        <v>727.29</v>
       </c>
       <c r="C4" t="n">
-        <v>470.49</v>
+        <v>594.89</v>
       </c>
       <c r="D4" t="n">
-        <v>29.28</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>136.08</v>
+        <v>164.37</v>
       </c>
       <c r="C5" t="n">
-        <v>119.09</v>
+        <v>144.2</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>594.23</v>
+        <v>501.59</v>
       </c>
       <c r="C6" t="n">
-        <v>566</v>
+        <v>451.7</v>
       </c>
       <c r="D6" t="n">
-        <v>34.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C7" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="D8" t="n">
-        <v>42.89</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112.04</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>71.90000000000001</v>
+        <v>60.99</v>
       </c>
       <c r="D9" t="n">
-        <v>43.07</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="10">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164.26</v>
+        <v>115.45</v>
       </c>
       <c r="C10" t="n">
-        <v>136.28</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>8.130000000000001</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="11">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>168.19</v>
+        <v>178.55</v>
       </c>
       <c r="C11" t="n">
-        <v>137.52</v>
+        <v>137.43</v>
       </c>
       <c r="D11" t="n">
-        <v>12.78</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="12">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>456.48</v>
+        <v>569.38</v>
       </c>
       <c r="C12" t="n">
-        <v>382.66</v>
+        <v>473.76</v>
       </c>
       <c r="D12" t="n">
-        <v>21.38</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="13">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.39</v>
+        <v>49.21</v>
       </c>
       <c r="C13" t="n">
-        <v>54.07</v>
+        <v>41.29</v>
       </c>
       <c r="D13" t="n">
-        <v>12.24</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="14">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>195.09</v>
+        <v>162.39</v>
       </c>
       <c r="C14" t="n">
-        <v>184.55</v>
+        <v>142.59</v>
       </c>
       <c r="D14" t="n">
-        <v>22.1</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="15">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54.77</v>
+        <v>75.97</v>
       </c>
       <c r="C15" t="n">
-        <v>38.75</v>
+        <v>57.53</v>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="16">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1902.53</v>
+        <v>953.3</v>
       </c>
       <c r="C16" t="n">
-        <v>1612.98</v>
+        <v>822.99</v>
       </c>
       <c r="D16" t="n">
-        <v>49.21</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="17">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>676.53</v>
+        <v>195.83</v>
       </c>
       <c r="C17" t="n">
-        <v>593.8099999999999</v>
+        <v>164.53</v>
       </c>
       <c r="D17" t="n">
-        <v>92.33</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="18">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>507.99</v>
+        <v>231.45</v>
       </c>
       <c r="C18" t="n">
-        <v>461.5</v>
+        <v>187.08</v>
       </c>
       <c r="D18" t="n">
-        <v>73.56999999999999</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="19">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>636.45</v>
+        <v>560.23</v>
       </c>
       <c r="C19" t="n">
-        <v>520.96</v>
+        <v>445.61</v>
       </c>
       <c r="D19" t="n">
-        <v>21.06</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>109.55</v>
+        <v>102.65</v>
       </c>
       <c r="C20" t="n">
-        <v>93.66</v>
+        <v>80.52</v>
       </c>
       <c r="D20" t="n">
-        <v>9.630000000000001</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="21">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>941.99</v>
+        <v>975.99</v>
       </c>
       <c r="C21" t="n">
-        <v>861.3200000000001</v>
+        <v>817.33</v>
       </c>
       <c r="D21" t="n">
-        <v>27.23</v>
+        <v>17.39</v>
       </c>
     </row>
   </sheetData>
